--- a/assets/data/经营模型与预算测算表.xlsx
+++ b/assets/data/经营模型与预算测算表.xlsx
@@ -482,7 +482,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>非快达 · 预算方案 v2（Gavin $10k/月全包含差旅；US$，¥/US$=7.1）</t>
+          <t>非快达 · 预算方案 v2.1（Gavin $7k/月全包含差旅；US$，¥/US$=7.1）</t>
         </is>
       </c>
     </row>
@@ -516,12 +516,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>一次性$60k + 峰值经营缺口$286k + 15%缓冲</t>
+          <t>一次性$60k + 峰值经营缺口$250k + 15%缓冲</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>≈$40万 ≈ ¥285万</t>
+          <t>≈$36万 ≈ ¥255万</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>零收入对冲：$506k + $60k</t>
+          <t>零收入对冲：$470k + $60k</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>≈$57万 ≈ ¥402万</t>
+          <t>≈$53万 ≈ ¥376万</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>峰值缺口$511k + $60k + 缓冲</t>
+          <t>峰值缺口$457k + $60k + 缓冲</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>≈$63万 ≈ ¥450万</t>
+          <t>≈$57万 ≈ ¥405万</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>覆盖③仍余约¥50万</t>
+          <t>覆盖③仍余约¥95万</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -644,6 +644,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -668,7 +669,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
     </row>
@@ -760,7 +761,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>30400</v>
+        <v>27400</v>
       </c>
       <c r="C12" s="3" t="inlineStr"/>
     </row>
@@ -830,7 +831,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>37400</v>
+        <v>34400</v>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
     </row>
@@ -856,7 +857,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
     </row>
@@ -1086,13 +1087,13 @@
         <v>2040</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>37400</v>
+        <v>34400</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-35360</v>
+        <v>-32360</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-35360</v>
+        <v>-32360</v>
       </c>
     </row>
     <row r="5">
@@ -1116,13 +1117,13 @@
         <v>3400</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>37400</v>
+        <v>34400</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-34000</v>
+        <v>-31000</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-69360</v>
+        <v>-63360</v>
       </c>
     </row>
     <row r="6">
@@ -1146,13 +1147,13 @@
         <v>5440</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>37400</v>
+        <v>34400</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-31960</v>
+        <v>-28960</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-101320</v>
+        <v>-92320</v>
       </c>
     </row>
     <row r="7">
@@ -1176,13 +1177,13 @@
         <v>8160</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>37400</v>
+        <v>34400</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-29240</v>
+        <v>-26240</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-130560</v>
+        <v>-118560</v>
       </c>
     </row>
     <row r="8">
@@ -1206,13 +1207,13 @@
         <v>10880</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>37400</v>
+        <v>34400</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-26520</v>
+        <v>-23520</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-157080</v>
+        <v>-142080</v>
       </c>
     </row>
     <row r="9">
@@ -1236,13 +1237,13 @@
         <v>13600</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>37400</v>
+        <v>34400</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-23800</v>
+        <v>-20800</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-180880</v>
+        <v>-162880</v>
       </c>
     </row>
     <row r="10">
@@ -1266,13 +1267,13 @@
         <v>17000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-29900</v>
+        <v>-26900</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-210780</v>
+        <v>-189780</v>
       </c>
     </row>
     <row r="11">
@@ -1296,13 +1297,13 @@
         <v>20400</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-26500</v>
+        <v>-23500</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-237280</v>
+        <v>-213280</v>
       </c>
     </row>
     <row r="12">
@@ -1326,13 +1327,13 @@
         <v>23800</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-23100</v>
+        <v>-20100</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-260380</v>
+        <v>-233380</v>
       </c>
     </row>
     <row r="13">
@@ -1356,13 +1357,13 @@
         <v>34000</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-12900</v>
+        <v>-9900</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-273280</v>
+        <v>-243280</v>
       </c>
     </row>
     <row r="14">
@@ -1386,13 +1387,13 @@
         <v>38250</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-8650</v>
+        <v>-5650</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-281930</v>
+        <v>-248930</v>
       </c>
     </row>
     <row r="15">
@@ -1416,13 +1417,13 @@
         <v>42500</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4400</v>
+        <v>-1400</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-286330</v>
+        <v>-250330</v>
       </c>
     </row>
     <row r="16">
@@ -1446,13 +1447,13 @@
         <v>46750</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-150</v>
+        <v>2850</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-286480</v>
+        <v>-247480</v>
       </c>
     </row>
     <row r="17">
@@ -1476,13 +1477,13 @@
         <v>48875</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1975</v>
+        <v>4975</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-284505</v>
+        <v>-242505</v>
       </c>
     </row>
     <row r="18">
@@ -1506,13 +1507,13 @@
         <v>51000</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4100</v>
+        <v>7100</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-280405</v>
+        <v>-235405</v>
       </c>
     </row>
     <row r="19">
@@ -1536,13 +1537,13 @@
         <v>53125</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>6225</v>
+        <v>9225</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-274180</v>
+        <v>-226180</v>
       </c>
     </row>
     <row r="20">
@@ -1566,13 +1567,13 @@
         <v>55250</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>8350</v>
+        <v>11350</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-265830</v>
+        <v>-214830</v>
       </c>
     </row>
     <row r="21">
@@ -1596,13 +1597,13 @@
         <v>57375</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>10475</v>
+        <v>13475</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-255355</v>
+        <v>-201355</v>
       </c>
     </row>
     <row r="22">
@@ -1626,13 +1627,13 @@
         <v>59500</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>12600</v>
+        <v>15600</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-242755</v>
+        <v>-185755</v>
       </c>
     </row>
     <row r="23">
@@ -1656,13 +1657,13 @@
         <v>59500</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>12600</v>
+        <v>15600</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-230155</v>
+        <v>-170155</v>
       </c>
     </row>
     <row r="24">
@@ -1686,13 +1687,13 @@
         <v>59500</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>12600</v>
+        <v>15600</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-217555</v>
+        <v>-154555</v>
       </c>
     </row>
     <row r="25">
@@ -1716,13 +1717,13 @@
         <v>59500</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>12600</v>
+        <v>15600</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-204955</v>
+        <v>-138955</v>
       </c>
     </row>
     <row r="26">
@@ -1746,13 +1747,13 @@
         <v>59500</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>12600</v>
+        <v>15600</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-192355</v>
+        <v>-123355</v>
       </c>
     </row>
     <row r="27">
@@ -1776,19 +1777,19 @@
         <v>59500</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>46900</v>
+        <v>43900</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>12600</v>
+        <v>15600</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-179755</v>
+        <v>-107755</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>峰值缺口(M13)</t>
+          <t>峰值缺口(M12)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr"/>
@@ -1798,7 +1799,7 @@
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="3" t="n">
-        <v>-286480</v>
+        <v>-250330</v>
       </c>
     </row>
     <row r="30">
@@ -1837,6 +1838,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1884,7 +1886,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -2102,7 +2104,7 @@
       <c r="B12" s="3" t="inlineStr"/>
       <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="3" t="n">
-        <v>30400</v>
+        <v>27400</v>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="3" t="inlineStr"/>
@@ -2142,7 +2144,7 @@
       <c r="B14" s="3" t="inlineStr"/>
       <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="n">
-        <v>39900</v>
+        <v>36900</v>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3" t="inlineStr"/>

--- a/assets/data/经营模型与预算测算表.xlsx
+++ b/assets/data/经营模型与预算测算表.xlsx
@@ -476,13 +476,13 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>非快达 · 预算方案 v2.1（Gavin $7k/月全包含差旅；US$，¥/US$=7.1）</t>
+          <t>非快达 · 预算方案 v3 定稿（轻量化7人；Gavin $8k全包；技术2人$7k；Token预留$1k；US$，¥/US$=7.1）</t>
         </is>
       </c>
     </row>
@@ -516,17 +516,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>一次性$60k + 峰值经营缺口$250k + 15%缓冲</t>
+          <t>一次性$65k + 峰值经营缺口$166k + 15%缓冲</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>≈$36万 ≈ ¥255万</t>
+          <t>≈$27万 ≈ ¥190万</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>基准爬坡下活到打平，零犯错余量</t>
+          <t>基准爬坡活到打平（M11），零犯错余量</t>
         </is>
       </c>
     </row>
@@ -538,12 +538,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>零收入对冲：$470k + $60k</t>
+          <t>零收入对冲：$377k + $65k</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>≈$53万 ≈ ¥376万</t>
+          <t>≈$44万 ≈ ¥315万</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -560,17 +560,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>峰值缺口$457k + $60k + 缓冲</t>
+          <t>峰值缺口$327k + $65k + 缓冲</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>≈$57万 ≈ ¥405万</t>
+          <t>≈$43万 ≈ ¥305万</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>保底¥500万的科学依据</t>
+          <t>暂缓扩编前提下</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>覆盖③仍余约¥95万</t>
+          <t>覆盖③仍余约¥195万</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>允许爬坡慢半年</t>
+          <t>允许爬坡慢半年且余量厚</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>基准+提前扩编+第二走廊+营运资金自持+24个月安全垫</t>
+          <t>基准+提前扩编+第二走廊+营运资金自持+安全垫</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -629,10 +629,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
@@ -644,7 +644,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -669,143 +668,147 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Kenya Country GM</t>
+          <t>走廊运营负责人</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>走廊运营负责人×2</t>
+          <t>调度客服×2</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr"/>
+        <v>1600</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>早晚班互备</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>调度客服×4</t>
+          <t>财务Controller（兼职）</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3200</v>
+        <v>1500</v>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>风控与索赔</t>
+          <t>工程师×2（远程，A后端/B前端）</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
+        <v>7000</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>董事会口径</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>财务Controller</t>
+          <t>本地法务retainer</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>全栈工程师×2（远程）</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>AI辅助编码</t>
-        </is>
-      </c>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>小计·人力（7人）</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>20600</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>本地法务retainer</t>
+          <t>Token 预留（数字员工矩阵）</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="C11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>实测预计M12约$780，见组织编制文档</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>小计·人力（11人）</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>27400</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>亚马逊云 AWS</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>技术与AI</t>
+          <t>GPS/地图</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Token $800起爬至$2,500/云/GPS/通信/SaaS</t>
-        </is>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>办公室</t>
+          <t>通信（WhatsApp/SMS/外呼）</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>团队差旅（Gavin除外）</t>
+          <t>SaaS/域名/企业邮箱</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>接待</t>
+          <t>办公室</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -816,50 +819,72 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>杂项</t>
+          <t>团队差旅（Gavin除外）</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>月度总烧钱 M0–M6</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>34400</v>
-      </c>
-      <c r="C18" s="3" t="inlineStr"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>接待</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>M7起扩编：产品1/AI工程1/销售2/口岸专员1</t>
+          <t>杂项</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>9500</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>与二期拨付/闸门挂钩，不达标冻结</t>
-        </is>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>月度总烧钱 M0–M6</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>26700</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>M7起扩编：GM/风控/销售×2/口岸/客服+1/财务转全职</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>与二期拨付/闸门挂钩</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>月度总烧钱 M7起</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>43900</v>
-      </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="n">
+        <v>36200</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -872,12 +897,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -944,54 +969,69 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>办公与设备</t>
+          <t>电脑设备</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>12000</v>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>MacBook Pro 64G ×3（Gavin+工程师×2）+ 外设</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>品牌与引流启动</t>
+          <t>办公押金与工位</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>正式域名官网/税费计算器/无坑问答/物料</t>
-        </is>
-      </c>
+        <v>5000</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>品牌与引流启动</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>含正式域名/官网/税费计算器/无坑问答/物料</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>平台MVP</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>自研+AI编程（外包对照价$30–50k）</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>60000</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1020,7 +1060,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>营收与现金曲线（基准：单均$850，贡献率8%→10%@M10）</t>
+          <t>营收与现金曲线（v3：单均$850，贡献率8%→10%@M10，月烧$26.7k/$36.2k）</t>
         </is>
       </c>
     </row>
@@ -1087,13 +1127,13 @@
         <v>2040</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>34400</v>
+        <v>26700</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-32360</v>
+        <v>-24660</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-32360</v>
+        <v>-24660</v>
       </c>
     </row>
     <row r="5">
@@ -1117,13 +1157,13 @@
         <v>3400</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>34400</v>
+        <v>26700</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-31000</v>
+        <v>-23300</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-63360</v>
+        <v>-47960</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1187,13 @@
         <v>5440</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>34400</v>
+        <v>26700</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-28960</v>
+        <v>-21260</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-92320</v>
+        <v>-69220</v>
       </c>
     </row>
     <row r="7">
@@ -1177,13 +1217,13 @@
         <v>8160</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>34400</v>
+        <v>26700</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-26240</v>
+        <v>-18540</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-118560</v>
+        <v>-87760</v>
       </c>
     </row>
     <row r="8">
@@ -1207,13 +1247,13 @@
         <v>10880</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>34400</v>
+        <v>26700</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-23520</v>
+        <v>-15820</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-142080</v>
+        <v>-103580</v>
       </c>
     </row>
     <row r="9">
@@ -1237,13 +1277,13 @@
         <v>13600</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>34400</v>
+        <v>26700</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-20800</v>
+        <v>-13100</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-162880</v>
+        <v>-116680</v>
       </c>
     </row>
     <row r="10">
@@ -1267,13 +1307,13 @@
         <v>17000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-26900</v>
+        <v>-19200</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-189780</v>
+        <v>-135880</v>
       </c>
     </row>
     <row r="11">
@@ -1297,13 +1337,13 @@
         <v>20400</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-23500</v>
+        <v>-15800</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-213280</v>
+        <v>-151680</v>
       </c>
     </row>
     <row r="12">
@@ -1327,13 +1367,13 @@
         <v>23800</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-20100</v>
+        <v>-12400</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-233380</v>
+        <v>-164080</v>
       </c>
     </row>
     <row r="13">
@@ -1357,13 +1397,13 @@
         <v>34000</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-9900</v>
+        <v>-2200</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-243280</v>
+        <v>-166280</v>
       </c>
     </row>
     <row r="14">
@@ -1387,13 +1427,13 @@
         <v>38250</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5650</v>
+        <v>2050</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-248930</v>
+        <v>-164230</v>
       </c>
     </row>
     <row r="15">
@@ -1417,13 +1457,13 @@
         <v>42500</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1400</v>
+        <v>6300</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-250330</v>
+        <v>-157930</v>
       </c>
     </row>
     <row r="16">
@@ -1447,13 +1487,13 @@
         <v>46750</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2850</v>
+        <v>10550</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-247480</v>
+        <v>-147380</v>
       </c>
     </row>
     <row r="17">
@@ -1477,13 +1517,13 @@
         <v>48875</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4975</v>
+        <v>12675</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-242505</v>
+        <v>-134705</v>
       </c>
     </row>
     <row r="18">
@@ -1507,13 +1547,13 @@
         <v>51000</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>7100</v>
+        <v>14800</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-235405</v>
+        <v>-119905</v>
       </c>
     </row>
     <row r="19">
@@ -1537,13 +1577,13 @@
         <v>53125</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>9225</v>
+        <v>16925</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-226180</v>
+        <v>-102980</v>
       </c>
     </row>
     <row r="20">
@@ -1567,13 +1607,13 @@
         <v>55250</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>11350</v>
+        <v>19050</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-214830</v>
+        <v>-83930</v>
       </c>
     </row>
     <row r="21">
@@ -1597,13 +1637,13 @@
         <v>57375</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>13475</v>
+        <v>21175</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-201355</v>
+        <v>-62755</v>
       </c>
     </row>
     <row r="22">
@@ -1627,13 +1667,13 @@
         <v>59500</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>15600</v>
+        <v>23300</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-185755</v>
+        <v>-39455</v>
       </c>
     </row>
     <row r="23">
@@ -1657,13 +1697,13 @@
         <v>59500</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>15600</v>
+        <v>23300</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-170155</v>
+        <v>-16155</v>
       </c>
     </row>
     <row r="24">
@@ -1687,13 +1727,13 @@
         <v>59500</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>15600</v>
+        <v>23300</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-154555</v>
+        <v>7145</v>
       </c>
     </row>
     <row r="25">
@@ -1717,13 +1757,13 @@
         <v>59500</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>15600</v>
+        <v>23300</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-138955</v>
+        <v>30445</v>
       </c>
     </row>
     <row r="26">
@@ -1747,13 +1787,13 @@
         <v>59500</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>15600</v>
+        <v>23300</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-123355</v>
+        <v>53745</v>
       </c>
     </row>
     <row r="27">
@@ -1777,19 +1817,19 @@
         <v>59500</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>43900</v>
+        <v>36200</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>15600</v>
+        <v>23300</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-107755</v>
+        <v>77045</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>峰值缺口(M12)</t>
+          <t>峰值缺口(M10)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr"/>
@@ -1799,13 +1839,13 @@
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="3" t="n">
-        <v>-250330</v>
+        <v>-166280</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>月度打平 M13–M14（≈550–575单）；Y1收入≈$2.46M，Y2≈$6.5M（与BP 2027 $6.3M咬合）；M12 500单仅为Sigma现有柜量约一半。</t>
+          <t>月度打平 M11（450单）；Y1收入≈$2.46M，Y2≈$6.5M（与BP 2027咬合）；M12 500单仅为Sigma现有柜量约一半。</t>
         </is>
       </c>
     </row>
@@ -1820,15 +1860,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1838,7 +1878,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1886,11 +1925,11 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>经营与数字化总负责；全包含差旅（董事会口径）</t>
+          <t>经营/产品/技术总负责；全包含差旅</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -1902,7 +1941,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Kenya Country GM</t>
+          <t>走廊运营负责人</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -1914,23 +1953,23 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>本地运营与政府关系</t>
+          <t>派单确认/异常处置/车队管理</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>荐车预警AI出人确认</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>走廊运营负责人</t>
+          <t>调度客服 A/B</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -1938,55 +1977,55 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>内罗毕/蒙巴萨</t>
+          <t>内罗毕</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>调度台/异常处置/车队</t>
+          <t>客户群5分钟响应；AI转单报价100%人工复核</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>荐车/预警AI出，人确认</t>
+          <t>转单/报价初稿AI出</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>调度与客服</t>
+          <t>财务Controller（兼职）</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>内罗毕</t>
+          <t>内罗毕/远程</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3200</v>
+        <v>1500</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>现场确认/POD/客户沟通</t>
+          <t>13周现金/对账/关联交易账</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>转单/报价初稿AI出</t>
+          <t>对账初稿AI出</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>风控与索赔</t>
+          <t>工程师 A（后端）</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -1994,27 +2033,27 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>内罗毕</t>
+          <t>远程</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1200</v>
+        <v>3500</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>授信/停单/索赔</t>
+          <t>交易内核/控制塔</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>夜间扫描AI跑</t>
+          <t>AI结对</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>财务Controller</t>
+          <t>工程师 B（前端）</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -2022,132 +2061,104 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>内罗毕(可兼)</t>
+          <t>远程</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>13周现金/对账/关联交易账</t>
+          <t>小程序/H5/追踪页</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>对账初稿AI出</t>
+          <t>AI结对</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>全栈工程师</t>
+          <t>法务顾问（retainer）</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>远程</t>
+          <t>内罗毕</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>交易内核自建</t>
+          <t>牌照/合同</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2人抵6–8人</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>法务顾问</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>retainer</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>牌照/合同</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>小计 M0–M6（7人）</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="n">
+        <v>20600</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>小计 M0–M6（11人）</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="n">
-        <v>27400</v>
-      </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>M7起扩编（触发表见组织编制文档）</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>GM/风控/销售×2/口岸/客服+1/财务全职</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>与闸门挂钩</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>M7–M12 增编 5 人</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="n">
-        <v>9500</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>产品/AI工程/销售×2/口岸专员</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>与闸门挂钩</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>小计 M7起（16人）</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr"/>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="n">
-        <v>36900</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>小计 M7起（13人）</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="n">
+        <v>30100</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/data/经营模型与预算测算表.xlsx
+++ b/assets/data/经营模型与预算测算表.xlsx
@@ -482,7 +482,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>非快达 · 预算方案 v3 定稿（轻量化7人；Gavin $8k全包；技术2人$7k；Token预留$1k；US$，¥/US$=7.1）</t>
+          <t>非快达 · 预算方案 v3.1 定稿（轻量化7人；Gavin $8k全包；工程师各$7k；Token预留$2k；US$，¥/US$=7.1）</t>
         </is>
       </c>
     </row>
@@ -516,17 +516,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>一次性$65k + 峰值经营缺口$166k + 15%缓冲</t>
+          <t>一次性$65k + 峰值经营缺口$254k + 15%缓冲</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>≈$27万 ≈ ¥190万</t>
+          <t>≈$37万 ≈ ¥260万</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>基准爬坡活到打平（M11），零犯错余量</t>
+          <t>基准爬坡活到打平（M13），零犯错余量</t>
         </is>
       </c>
     </row>
@@ -538,12 +538,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>零收入对冲：$377k + $65k</t>
+          <t>零收入对冲：$473k + $65k</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>≈$44万 ≈ ¥315万</t>
+          <t>≈$54万 ≈ ¥382万</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>峰值缺口$327k + $65k + 缓冲</t>
+          <t>峰值缺口$462k + $65k + 缓冲</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>≈$43万 ≈ ¥305万</t>
+          <t>≈$58万 ≈ ¥412万</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>覆盖③仍余约¥195万</t>
+          <t>覆盖③仍余约¥88万</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>允许爬坡慢半年且余量厚</t>
+          <t>容错线成立，余量收窄，爬坡纪律必须顶住</t>
         </is>
       </c>
     </row>
@@ -644,6 +644,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -712,11 +713,11 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>工程师×2（远程，A后端/B前端）</t>
+          <t>工程师×2（中国市场价各$7k，A后端/B前端）</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>7000</v>
+        <v>14000</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -742,7 +743,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>20600</v>
+        <v>27600</v>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
     </row>
@@ -753,7 +754,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -856,7 +857,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>26700</v>
+        <v>34700</v>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
     </row>
@@ -882,7 +883,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
     </row>
@@ -1060,7 +1061,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>营收与现金曲线（v3：单均$850，贡献率8%→10%@M10，月烧$26.7k/$36.2k）</t>
+          <t>营收与现金曲线（v3.1：单均$850，贡献率8%→10%@M10，月烧$34.7k/$44.2k）</t>
         </is>
       </c>
     </row>
@@ -1127,13 +1128,13 @@
         <v>2040</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>26700</v>
+        <v>34700</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-24660</v>
+        <v>-32660</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-24660</v>
+        <v>-32660</v>
       </c>
     </row>
     <row r="5">
@@ -1157,13 +1158,13 @@
         <v>3400</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>26700</v>
+        <v>34700</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-23300</v>
+        <v>-31300</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-47960</v>
+        <v>-63960</v>
       </c>
     </row>
     <row r="6">
@@ -1187,13 +1188,13 @@
         <v>5440</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>26700</v>
+        <v>34700</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-21260</v>
+        <v>-29260</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-69220</v>
+        <v>-93220</v>
       </c>
     </row>
     <row r="7">
@@ -1217,13 +1218,13 @@
         <v>8160</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>26700</v>
+        <v>34700</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-18540</v>
+        <v>-26540</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-87760</v>
+        <v>-119760</v>
       </c>
     </row>
     <row r="8">
@@ -1247,13 +1248,13 @@
         <v>10880</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>26700</v>
+        <v>34700</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-15820</v>
+        <v>-23820</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-103580</v>
+        <v>-143580</v>
       </c>
     </row>
     <row r="9">
@@ -1277,13 +1278,13 @@
         <v>13600</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>26700</v>
+        <v>34700</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-13100</v>
+        <v>-21100</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-116680</v>
+        <v>-164680</v>
       </c>
     </row>
     <row r="10">
@@ -1307,13 +1308,13 @@
         <v>17000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-19200</v>
+        <v>-27200</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-135880</v>
+        <v>-191880</v>
       </c>
     </row>
     <row r="11">
@@ -1337,13 +1338,13 @@
         <v>20400</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-15800</v>
+        <v>-23800</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-151680</v>
+        <v>-215680</v>
       </c>
     </row>
     <row r="12">
@@ -1367,13 +1368,13 @@
         <v>23800</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-12400</v>
+        <v>-20400</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-164080</v>
+        <v>-236080</v>
       </c>
     </row>
     <row r="13">
@@ -1397,13 +1398,13 @@
         <v>34000</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2200</v>
+        <v>-10200</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-166280</v>
+        <v>-246280</v>
       </c>
     </row>
     <row r="14">
@@ -1427,13 +1428,13 @@
         <v>38250</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2050</v>
+        <v>-5950</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-164230</v>
+        <v>-252230</v>
       </c>
     </row>
     <row r="15">
@@ -1457,13 +1458,13 @@
         <v>42500</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>6300</v>
+        <v>-1700</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-157930</v>
+        <v>-253930</v>
       </c>
     </row>
     <row r="16">
@@ -1487,13 +1488,13 @@
         <v>46750</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>10550</v>
+        <v>2550</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-147380</v>
+        <v>-251380</v>
       </c>
     </row>
     <row r="17">
@@ -1517,13 +1518,13 @@
         <v>48875</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>12675</v>
+        <v>4675</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-134705</v>
+        <v>-246705</v>
       </c>
     </row>
     <row r="18">
@@ -1547,13 +1548,13 @@
         <v>51000</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>14800</v>
+        <v>6800</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-119905</v>
+        <v>-239905</v>
       </c>
     </row>
     <row r="19">
@@ -1577,13 +1578,13 @@
         <v>53125</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>16925</v>
+        <v>8925</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-102980</v>
+        <v>-230980</v>
       </c>
     </row>
     <row r="20">
@@ -1607,13 +1608,13 @@
         <v>55250</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>19050</v>
+        <v>11050</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-83930</v>
+        <v>-219930</v>
       </c>
     </row>
     <row r="21">
@@ -1637,13 +1638,13 @@
         <v>57375</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>21175</v>
+        <v>13175</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-62755</v>
+        <v>-206755</v>
       </c>
     </row>
     <row r="22">
@@ -1667,13 +1668,13 @@
         <v>59500</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>23300</v>
+        <v>15300</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-39455</v>
+        <v>-191455</v>
       </c>
     </row>
     <row r="23">
@@ -1697,13 +1698,13 @@
         <v>59500</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>23300</v>
+        <v>15300</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-16155</v>
+        <v>-176155</v>
       </c>
     </row>
     <row r="24">
@@ -1727,13 +1728,13 @@
         <v>59500</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>23300</v>
+        <v>15300</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>7145</v>
+        <v>-160855</v>
       </c>
     </row>
     <row r="25">
@@ -1757,13 +1758,13 @@
         <v>59500</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>23300</v>
+        <v>15300</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>30445</v>
+        <v>-145555</v>
       </c>
     </row>
     <row r="26">
@@ -1787,13 +1788,13 @@
         <v>59500</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>23300</v>
+        <v>15300</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>53745</v>
+        <v>-130255</v>
       </c>
     </row>
     <row r="27">
@@ -1817,19 +1818,19 @@
         <v>59500</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>36200</v>
+        <v>44200</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>23300</v>
+        <v>15300</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>77045</v>
+        <v>-114955</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>峰值缺口(M10)</t>
+          <t>峰值缺口(M12)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr"/>
@@ -1839,7 +1840,7 @@
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="3" t="n">
-        <v>-166280</v>
+        <v>-253930</v>
       </c>
     </row>
     <row r="30">
@@ -1878,6 +1879,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2033,11 +2035,11 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>远程</t>
+          <t>中国/远程</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3500</v>
+        <v>7000</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2061,11 +2063,11 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>远程</t>
+          <t>中国/远程</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3500</v>
+        <v>7000</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -2115,7 +2117,7 @@
       <c r="B11" s="3" t="inlineStr"/>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="n">
-        <v>20600</v>
+        <v>27600</v>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
@@ -2155,7 +2157,7 @@
       <c r="B13" s="3" t="inlineStr"/>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="n">
-        <v>30100</v>
+        <v>37100</v>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
